--- a/middleware/data/SportsFest_2026_Venue_Input_Template.xlsx
+++ b/middleware/data/SportsFest_2026_Venue_Input_Template.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Venue-Input" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gym-Modes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Playoff-Slots" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,21 +427,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,40 +469,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Last Start Time</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Slot Minutes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Available Slots</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Exclusive Venue Group</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -507,219 +521,529 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>North OC Tennis Pod</t>
+          <t>Main Gym</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>City Park</t>
+          <t>Church Main Gym</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tennis Court</t>
+          <t>Basketball Court</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Sat-1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>13</v>
-      </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="n">
         <v>60</v>
       </c>
-      <c r="I2">
-        <f>D2*(((G2-F2)*60/H2)+1)</f>
+      <c r="J2">
+        <f>D2*(((H2-G2)*60/I2)+1)</f>
         <v/>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Main Gym</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Staff verified usable</t>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>BB or VB — set Gym-Modes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pickleball Pod A</t>
+          <t>Main Gym</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Community Center</t>
+          <t>Church Main Gym</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pickleball Court</t>
+          <t>Volleyball Court</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Sat-1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>13</v>
-      </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>45</v>
-      </c>
-      <c r="I3">
-        <f>D3*(((G3-F3)*60/H3)+1)</f>
+        <v>20</v>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J3">
+        <f>D3*(((H3-G3)*60/I3)+1)</f>
         <v/>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Main Gym</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Includes 35+</t>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>BB or VB — set Gym-Modes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Indoor Table Pod</t>
+          <t>North OC Tennis Pod</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Church Hall</t>
+          <t>City Park</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Table Tennis Table</t>
+          <t>Tennis Court</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Sun-1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" t="n">
         <v>18</v>
       </c>
-      <c r="G4" t="n">
-        <v>21</v>
-      </c>
-      <c r="H4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4">
-        <f>D4*(((G4-F4)*60/H4)+1)</f>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4">
+        <f>D4*(((H4-G4)*60/I4)+1)</f>
         <v/>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Includes 35+</t>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Staff verified usable</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Badminton Pod</t>
+          <t>Pickleball Pod A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>School Gym</t>
+          <t>Community Center</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Badminton Court</t>
+          <t>Pickleball Court</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Sun-1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="n">
         <v>18</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
+        <v>45</v>
+      </c>
+      <c r="J5">
+        <f>D5*(((H5-G5)*60/I5)+1)</f>
+        <v/>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Includes 35+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Indoor Table Pod</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Church Hall</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Table Tennis Table</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sun-2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>18</v>
+      </c>
+      <c r="H6" t="n">
         <v>21</v>
       </c>
-      <c r="H5" t="n">
-        <v>45</v>
-      </c>
-      <c r="I5">
-        <f>D5*(((G5-F5)*60/H5)+1)</f>
+      <c r="I6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <f>D6*(((H6-G6)*60/I6)+1)</f>
         <v/>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Staff verified usable</t>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Includes 35+</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Available Slots formula: =D*(((G-F)*60/H)+1) where D=Quantity, F=Start Time (decimal hour), G=Last Start Time (decimal hour), H=Slot Minutes. Add one row per pod per date. Staff-entered resources are assumed valid.</t>
+          <t>Badminton Pod</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>School Gym</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Badminton Court</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sun-2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I7" t="n">
+        <v>45</v>
+      </c>
+      <c r="J7">
+        <f>D7*(((H7-G7)*60/I7)+1)</f>
+        <v/>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Staff verified usable</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Available Slots formula: =D*(((H-G)*60/I)+1). Day: Sat-1, Sun-1, Sat-2, Sun-2. Exclusive Venue Group: same label on gym rows sharing a physical gym.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gym Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Basketball Courts</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Volleyball Courts</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Badminton Courts</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pickleball Courts</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Soccer Fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Main Gym</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Side Gym</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gym Name must match Exclusive Venue Group in Venue-Input. Enter courts per mode (0 = not available).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>game_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>resource_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Add one row per playoff game. resource_id and slot must match generated values.</t>
         </is>
       </c>
     </row>

--- a/middleware/data/SportsFest_2026_Venue_Input_Template.xlsx
+++ b/middleware/data/SportsFest_2026_Venue_Input_Template.xlsx
@@ -686,7 +686,6 @@
         <f>D4*(((H4-G4)*60/I4)+1)</f>
         <v/>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -745,7 +744,6 @@
         <f>D5*(((H5-G5)*60/I5)+1)</f>
         <v/>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -804,7 +802,6 @@
         <f>D6*(((H6-G6)*60/I6)+1)</f>
         <v/>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -863,7 +860,6 @@
         <f>D7*(((H7-G7)*60/I7)+1)</f>
         <v/>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1003,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1014,27 +1010,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>game_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gym_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>start_time</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>slot_minutes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>resource_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>slot</t>
         </is>
@@ -1043,7 +1059,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Add one row per playoff game. resource_id and slot must match generated values.</t>
+          <t>Add one row per playoff game. Preferred: fill gym_name + date + start_time (values from Venue-Input). Legacy/override: resource_id + slot must match generated Schedule-Input values.</t>
         </is>
       </c>
     </row>
